--- a/accountant-skill/data/output/Oct2025/audit_validation_Oct2025.xlsx
+++ b/accountant-skill/data/output/Oct2025/audit_validation_Oct2025.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,10 +59,6 @@
     <font>
       <name val="Arial"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -120,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -160,13 +156,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -535,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -606,7 +599,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -618,11 +611,11 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -638,7 +631,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -675,7 +668,7 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -730,38 +723,15 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Assets=449,450,729.09, Equity=449,450,729.09, Liabilities=nan, Diff=nan</t>
+          <t>Assets=1,460,294,322.80, Equity=1,460,294,322.80, Liabilities=0.00, Diff=0.00</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Financial Validation</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Balance Sheet (Dashboard Check)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Dashboard validation: PASS</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -785,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -845,29 +815,12 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Assets=449,450,729.09, Equity=449,450,729.09, Liabilities=nan, Diff=nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Balance Sheet (Dashboard Check)</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Dashboard validation: PASS</t>
+          <t>Assets=1,460,294,322.80, Equity=1,460,294,322.80, Liabilities=0.00, Diff=0.00</t>
         </is>
       </c>
     </row>
@@ -888,14 +841,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -944,27 +897,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Financial Validation</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Balance Sheet: Assets = Equity + Liabilities</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Assets=449,450,729.09, Equity=449,450,729.09, Liabilities=nan, Diff=nan</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Data Load</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Module 3</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Module 3: bank_reconciliation*.xlsx not found</t>
         </is>
       </c>
     </row>
@@ -979,7 +932,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Module 4</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -988,31 +941,6 @@
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Module 3: bank_reconciliation*.xlsx not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Data Load</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Module 4</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Module 4: adjusting_entries*.xlsx not found</t>
         </is>

--- a/accountant-skill/data/output/Oct2025/audit_validation_Oct2025.xlsx
+++ b/accountant-skill/data/output/Oct2025/audit_validation_Oct2025.xlsx
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01 to 2025-10-31</t>
+          <t>2025-Oct-01 to 2025-Oct-31</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Assets=1,460,294,322.80, Equity=1,460,294,322.80, Liabilities=0.00, Diff=0.00</t>
+          <t>Assets=1,899,825,145.80, Equity=1,899,825,145.80, Liabilities=0.00, Diff=0.00</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr"/>
@@ -785,7 +785,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01 to 2025-10-31</t>
+          <t>2025-Oct-01 to 2025-Oct-31</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Assets=1,460,294,322.80, Equity=1,460,294,322.80, Liabilities=0.00, Diff=0.00</t>
+          <t>Assets=1,899,825,145.80, Equity=1,899,825,145.80, Liabilities=0.00, Diff=0.00</t>
         </is>
       </c>
     </row>

--- a/accountant-skill/data/output/Oct2025/audit_validation_Oct2025.xlsx
+++ b/accountant-skill/data/output/Oct2025/audit_validation_Oct2025.xlsx
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct-01 to 2025-Oct-31</t>
+          <t>2025-10-01 to 2025-10-31</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct-01 to 2025-Oct-31</t>
+          <t>2025-10-01 to 2025-10-31</t>
         </is>
       </c>
     </row>
